--- a/data/trans_orig/P1429-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P1429-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de osteoporosis en 2007</t>
+          <t>Población con diagnóstico de osteoporosis en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1897</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,82 +748,82 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>3636</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>923</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>9151</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,78%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>1,96%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>3636</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>907</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>8252</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
           <t>0,38%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>3636</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>918</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>8216</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,78%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>1,76%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>3636</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>926</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>9048</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,86%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>492167</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>494064</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,82 +861,82 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>485</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>463853</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>458338</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>466566</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>99,22%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>98,04%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>99,8%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>984</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>957917</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>953301</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>960646</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
           <t>99,62%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>485</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>463853</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>459273</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>466571</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,22%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>98,24%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>99,8%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>984</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>957917</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>952505</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>960627</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>99,62%</t>
-        </is>
-      </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,9%</t>
+          <t>99,91%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>999</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12044</t>
+          <t>10463</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6780</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1968</t>
+          <t>1985</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12502</t>
+          <t>12933</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,95%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>723445</t>
+          <t>725026</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>734485</t>
+          <t>734490</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>618714</t>
+          <t>619590</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1348480</t>
+          <t>1348049</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1359014</t>
+          <t>1358997</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,85%</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7655</t>
+          <t>7407</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1974</t>
+          <t>1967</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11268</t>
+          <t>11960</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3121</t>
+          <t>3213</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15464</t>
+          <t>14509</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,09%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>631013</t>
+          <t>631261</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>678476</t>
+          <t>677784</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>687770</t>
+          <t>687777</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1312948</t>
+          <t>1313903</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1325291</t>
+          <t>1325199</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,76%</t>
         </is>
       </c>
     </row>
@@ -1767,7 +1767,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6434</t>
+          <t>6337</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8269</t>
+          <t>7873</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23746</t>
+          <t>22416</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9531</t>
+          <t>10029</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25165</t>
+          <t>26282</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>512713</t>
+          <t>512810</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>491896</t>
+          <t>493226</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>507373</t>
+          <t>507769</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1009624</t>
+          <t>1008507</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1025258</t>
+          <t>1024760</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,03%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3107</t>
+          <t>3424</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14875</t>
+          <t>14335</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>24115</t>
+          <t>24346</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>46979</t>
+          <t>46194</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>29563</t>
+          <t>29872</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>54266</t>
+          <t>56827</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,19%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>371835</t>
+          <t>372375</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>383603</t>
+          <t>383286</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>357007</t>
+          <t>357792</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>379871</t>
+          <t>379640</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,37%</t>
+          <t>88,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>736430</t>
+          <t>733869</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>761133</t>
+          <t>760824</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,22%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4392</t>
+          <t>3871</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15592</t>
+          <t>15718</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>30435</t>
+          <t>30945</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>53128</t>
+          <t>53696</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>38622</t>
+          <t>38308</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>64167</t>
+          <t>64683</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,18%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>276991</t>
+          <t>276865</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>288191</t>
+          <t>288712</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>289806</t>
+          <t>289238</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>312499</t>
+          <t>311989</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>84,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>90,98%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>571350</t>
+          <t>570834</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>596895</t>
+          <t>597209</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>89,82%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>93,97%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5185</t>
+          <t>5221</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17155</t>
+          <t>17101</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>32548</t>
+          <t>33888</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>60823</t>
+          <t>61212</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>42314</t>
+          <t>40224</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>71911</t>
+          <t>70706</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,0%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>192728</t>
+          <t>192782</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>204698</t>
+          <t>204662</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>273085</t>
+          <t>272696</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>301360</t>
+          <t>300020</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>81,78%</t>
+          <t>81,67%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>89,85%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>471880</t>
+          <t>473085</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>501477</t>
+          <t>503567</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>86,78%</t>
+          <t>87,0%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>92,6%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>23203</t>
+          <t>24797</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>45780</t>
+          <t>48276</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>122035</t>
+          <t>121146</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>169587</t>
+          <t>169092</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>155574</t>
+          <t>153714</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>206337</t>
+          <t>207773</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3230763</t>
+          <t>3228267</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3253340</t>
+          <t>3251746</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3209610</t>
+          <t>3210105</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3257162</t>
+          <t>3258051</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6449404</t>
+          <t>6447968</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6500167</t>
+          <t>6502027</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,69%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de osteoporosis en 2012</t>
+          <t>Población con diagnóstico de osteoporosis en 2012 (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,97 +3712,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1951</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1957</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>1956</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>452195</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>454146</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>428273</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>430230</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>882420</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>884376</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1975</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>946</t>
+          <t>950</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12586</t>
+          <t>12388</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>946</t>
+          <t>943</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12393</t>
+          <t>12148</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>685112</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>687087</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>597669</t>
+          <t>597867</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>609309</t>
+          <t>609305</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>99,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1284949</t>
+          <t>1285194</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1296396</t>
+          <t>1296399</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4398,97 +4398,97 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1932</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2008</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>6788</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>0,96%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>1932</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>6808</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>5988</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,14%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>0,96%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>1932</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>5876</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,14%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,43%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>679855</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>681863</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>702766</t>
+          <t>702786</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1385561</t>
+          <t>1385449</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4746,7 +4746,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5455</t>
+          <t>5067</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7330</t>
+          <t>8030</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22203</t>
+          <t>23565</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8306</t>
+          <t>8333</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>23284</t>
+          <t>23995</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -4854,7 +4854,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>609162</t>
+          <t>609550</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>592061</t>
+          <t>590699</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>606934</t>
+          <t>606234</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1205596</t>
+          <t>1204885</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1220574</t>
+          <t>1220547</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5665</t>
+          <t>4941</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>25006</t>
+          <t>25450</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>48323</t>
+          <t>48169</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>26298</t>
+          <t>25756</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>50678</t>
+          <t>50584</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,77%</t>
         </is>
       </c>
     </row>
@@ -5197,7 +5197,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>423764</t>
+          <t>424488</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>399477</t>
+          <t>399631</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>422794</t>
+          <t>422350</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>826551</t>
+          <t>826645</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>850931</t>
+          <t>851473</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>97,06%</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5408</t>
+          <t>5300</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>21227</t>
+          <t>21970</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>44045</t>
+          <t>44608</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>22936</t>
+          <t>21596</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>46785</t>
+          <t>44662</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,73%</t>
         </is>
       </c>
     </row>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>304378</t>
+          <t>304486</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5555,7 +5555,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>309951</t>
+          <t>309388</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>332769</t>
+          <t>332026</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>87,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>616997</t>
+          <t>619120</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>640846</t>
+          <t>642186</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,75%</t>
         </is>
       </c>
     </row>
@@ -5775,7 +5775,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>12224</t>
+          <t>13591</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>41868</t>
+          <t>41678</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>71049</t>
+          <t>69509</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>43607</t>
+          <t>44041</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>74374</t>
+          <t>74666</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,73%</t>
         </is>
       </c>
     </row>
@@ -5883,7 +5883,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>236624</t>
+          <t>235257</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -5898,7 +5898,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>316821</t>
+          <t>318361</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>346002</t>
+          <t>346192</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>81,68%</t>
+          <t>82,08%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>562344</t>
+          <t>562052</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>593111</t>
+          <t>592677</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>88,32%</t>
+          <t>88,27%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,08%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2077</t>
+          <t>2057</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>15463</t>
+          <t>15112</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>120743</t>
+          <t>119238</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>169238</t>
+          <t>170426</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>125074</t>
+          <t>123147</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>175682</t>
+          <t>174630</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3410313</t>
+          <t>3410664</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3423699</t>
+          <t>3423719</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,7 +6241,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3384752</t>
+          <t>3383564</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3433247</t>
+          <t>3434752</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6804084</t>
+          <t>6805136</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6854692</t>
+          <t>6856619</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,24%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de osteoporosis en 2016</t>
+          <t>Población con diagnóstico de osteoporosis en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6691,97 +6691,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2044</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1876</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>1962</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>417419</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>419463</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>393879</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>395755</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>813256</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>815218</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7034,97 +7034,97 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>1996</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>1866</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>1932</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>588500</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>590496</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>561678</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>563544</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1152108</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1154040</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7382,7 +7382,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4636</t>
+          <t>5376</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7397,7 +7397,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>931</t>
+          <t>935</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9381</t>
+          <t>8501</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7432,7 +7432,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1821</t>
+          <t>1843</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9571</t>
+          <t>9824</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7467,7 +7467,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>
@@ -7490,7 +7490,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>664461</t>
+          <t>663721</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -7505,7 +7505,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>652005</t>
+          <t>652885</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>660455</t>
+          <t>660451</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1320912</t>
+          <t>1320659</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1328662</t>
+          <t>1328640</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,7 +7575,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -7725,7 +7725,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7842</t>
+          <t>7287</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7740,7 +7740,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3197</t>
+          <t>3208</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13874</t>
+          <t>15369</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7775,7 +7775,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5195</t>
+          <t>5257</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18295</t>
+          <t>19035</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -7833,7 +7833,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>638206</t>
+          <t>638761</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -7848,7 +7848,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>635203</t>
+          <t>633708</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>645880</t>
+          <t>645869</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,7 +7883,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1276830</t>
+          <t>1276090</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1289930</t>
+          <t>1289868</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,59%</t>
         </is>
       </c>
     </row>
@@ -8068,7 +8068,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7778</t>
+          <t>6700</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8083,7 +8083,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14106</t>
+          <t>14045</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>34162</t>
+          <t>34520</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15784</t>
+          <t>15457</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>36837</t>
+          <t>36546</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,75%</t>
         </is>
       </c>
     </row>
@@ -8176,7 +8176,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>470140</t>
+          <t>471218</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -8191,7 +8191,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>462687</t>
+          <t>462329</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>482743</t>
+          <t>482804</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>937930</t>
+          <t>938221</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>958983</t>
+          <t>959310</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,41%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1969</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>33042</t>
+          <t>33515</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>58144</t>
+          <t>58084</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>33031</t>
+          <t>32289</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>58499</t>
+          <t>59189</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,31%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>332361</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>334330</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>319618</t>
+          <t>319678</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>344720</t>
+          <t>344247</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>84,61%</t>
+          <t>84,62%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,13%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>653593</t>
+          <t>652903</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>679061</t>
+          <t>679803</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,47%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2637</t>
+          <t>2706</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13104</t>
+          <t>12355</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>31491</t>
+          <t>31090</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>60402</t>
+          <t>60895</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>36486</t>
+          <t>37397</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>67044</t>
+          <t>66696</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,15%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>243894</t>
+          <t>244643</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>254361</t>
+          <t>254292</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>339767</t>
+          <t>339274</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>368678</t>
+          <t>369079</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>84,78%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>590123</t>
+          <t>590471</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>620681</t>
+          <t>619770</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>89,85%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,31%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6221</t>
+          <t>6004</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>19915</t>
+          <t>20052</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>100609</t>
+          <t>101099</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>150165</t>
+          <t>147982</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>111233</t>
+          <t>112228</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>159405</t>
+          <t>159314</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,7 +9177,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3374435</t>
+          <t>3374298</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3388129</t>
+          <t>3388346</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3394377</t>
+          <t>3396560</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3443933</t>
+          <t>3443443</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6779487</t>
+          <t>6779578</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6827659</t>
+          <t>6826664</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9295,7 +9295,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,38%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de osteoporosis en 2023</t>
+          <t>Población con diagnóstico de osteoporosis en 2023 (tasa de respuesta: 99,68%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9675,7 +9675,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20686</t>
+          <t>22398</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9710,7 +9710,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14369</t>
+          <t>13620</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9745,7 +9745,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23768</t>
+          <t>22833</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,2%</t>
         </is>
       </c>
     </row>
@@ -9783,7 +9783,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>379301</t>
+          <t>377589</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -9798,7 +9798,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -9818,7 +9818,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>298831</t>
+          <t>299580</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -9833,7 +9833,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -9853,7 +9853,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>689419</t>
+          <t>690354</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -9868,7 +9868,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -10013,97 +10013,97 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2683</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>2130</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>2353</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>420864</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>509374</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>932698</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -10361,7 +10361,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6667</t>
+          <t>7616</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10376,7 +10376,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>459</t>
+          <t>462</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5182</t>
+          <t>4688</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1438</t>
+          <t>1183</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9511</t>
+          <t>8731</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,81%</t>
         </is>
       </c>
     </row>
@@ -10469,7 +10469,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>528350</t>
+          <t>527401</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -10484,7 +10484,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>535846</t>
+          <t>536340</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>540569</t>
+          <t>540566</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,92%</t>
+          <t>99,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1066533</t>
+          <t>1067313</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1074606</t>
+          <t>1074861</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>99,89%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7840</t>
+          <t>8368</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6299</t>
+          <t>6519</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15771</t>
+          <t>15585</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10774,7 +10774,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>20260</t>
+          <t>20336</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>877841</t>
+          <t>877313</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>885111</t>
+          <t>885681</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,94%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>693657</t>
+          <t>693843</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>703129</t>
+          <t>702909</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,7 +10882,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1574849</t>
+          <t>1574773</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2324</t>
+          <t>2378</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11330</t>
+          <t>11318</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,7 +11057,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>27786</t>
+          <t>27637</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>44992</t>
+          <t>44467</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>31604</t>
+          <t>32272</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>51343</t>
+          <t>51541</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,68%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>548907</t>
+          <t>548919</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>557913</t>
+          <t>557859</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11175,7 +11175,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>496521</t>
+          <t>497046</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>513727</t>
+          <t>513876</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1050407</t>
+          <t>1050209</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1070146</t>
+          <t>1069478</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,07%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3080</t>
+          <t>3089</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10787</t>
+          <t>10671</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11405,7 +11405,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15541</t>
+          <t>16113</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>66895</t>
+          <t>65264</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>21489</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>63389</t>
+          <t>63585</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,54%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>355395</t>
+          <t>355511</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>363102</t>
+          <t>363093</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,7 +11513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>539718</t>
+          <t>541349</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>591072</t>
+          <t>590500</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>909407</t>
+          <t>909211</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>951307</t>
+          <t>948700</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,52%</t>
         </is>
       </c>
     </row>
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4320</t>
+          <t>4227</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>12991</t>
+          <t>13342</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11763,7 +11763,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>58978</t>
+          <t>59500</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>66680</t>
+          <t>66457</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>90705</t>
+          <t>90083</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,76%</t>
         </is>
       </c>
     </row>
@@ -11841,12 +11841,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>269141</t>
+          <t>268790</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>277812</t>
+          <t>277905</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11881,7 +11881,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>365076</t>
+          <t>364554</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11896,7 +11896,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>86,09%</t>
+          <t>85,97%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>615481</t>
+          <t>616103</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>639506</t>
+          <t>639729</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>87,24%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>90,59%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>19140</t>
+          <t>19725</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>44762</t>
+          <t>45696</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>130962</t>
+          <t>133684</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>183702</t>
+          <t>182674</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>162971</t>
+          <t>160015</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>215511</t>
+          <t>212931</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,0%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3408021</t>
+          <t>3407087</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3433643</t>
+          <t>3433058</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3463638</t>
+          <t>3464666</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3516378</t>
+          <t>3513656</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,17 +12249,17 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>6911350</t>
+          <t>6911351</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6884612</t>
+          <t>6887193</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6937152</t>
+          <t>6940109</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,75%</t>
         </is>
       </c>
     </row>
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7100123</t>
+          <t>7100124</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7100123</t>
+          <t>7100124</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7100123</t>
+          <t>7100124</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">

--- a/data/trans_orig/P1429-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P1429-Edad-trans_orig.xlsx
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>923</t>
+          <t>918</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9151</t>
+          <t>9161</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>907</t>
+          <t>908</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8252</t>
+          <t>9105</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,95%</t>
         </is>
       </c>
     </row>
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>458338</t>
+          <t>458328</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>466566</t>
+          <t>466571</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>953301</t>
+          <t>952448</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>960646</t>
+          <t>960645</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10463</t>
+          <t>11640</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>7382</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1985</t>
+          <t>2123</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12933</t>
+          <t>16056</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>725026</t>
+          <t>723849</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>619590</t>
+          <t>618112</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1348049</t>
+          <t>1344926</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1358997</t>
+          <t>1358859</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>99,84%</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7407</t>
+          <t>7515</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1967</t>
+          <t>1965</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11960</t>
+          <t>11737</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3213</t>
+          <t>3039</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14509</t>
+          <t>15225</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>631261</t>
+          <t>631153</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>677784</t>
+          <t>678007</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>687777</t>
+          <t>687779</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1313903</t>
+          <t>1313187</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1325199</t>
+          <t>1325373</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,77%</t>
         </is>
       </c>
     </row>
@@ -1767,7 +1767,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6337</t>
+          <t>5640</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7873</t>
+          <t>8014</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22416</t>
+          <t>22619</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10029</t>
+          <t>9793</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>26282</t>
+          <t>25614</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>512810</t>
+          <t>513507</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>493226</t>
+          <t>493023</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>507769</t>
+          <t>507628</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1008507</t>
+          <t>1009175</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1024760</t>
+          <t>1024996</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,05%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3424</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14335</t>
+          <t>15234</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>24346</t>
+          <t>24584</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>46194</t>
+          <t>46829</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>29872</t>
+          <t>28964</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>56827</t>
+          <t>55958</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,08%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>372375</t>
+          <t>371476</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>383286</t>
+          <t>383563</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>357792</t>
+          <t>357157</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>379640</t>
+          <t>379402</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>88,41%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>733869</t>
+          <t>734738</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>760824</t>
+          <t>761732</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,34%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3871</t>
+          <t>3827</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15718</t>
+          <t>15432</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>30945</t>
+          <t>30200</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>53696</t>
+          <t>53296</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>38308</t>
+          <t>37824</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>64683</t>
+          <t>65236</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,26%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>276865</t>
+          <t>277151</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>288712</t>
+          <t>288756</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>289238</t>
+          <t>289638</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>311989</t>
+          <t>312734</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>84,34%</t>
+          <t>84,46%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>570834</t>
+          <t>570281</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>597209</t>
+          <t>597693</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>89,74%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>94,05%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5221</t>
+          <t>5316</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17101</t>
+          <t>17473</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>33888</t>
+          <t>32905</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>61212</t>
+          <t>59247</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>40224</t>
+          <t>41982</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>70706</t>
+          <t>72968</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,42%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>192782</t>
+          <t>192410</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>204662</t>
+          <t>204567</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>272696</t>
+          <t>274661</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>300020</t>
+          <t>301003</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>81,67%</t>
+          <t>82,26%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>473085</t>
+          <t>470823</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>503567</t>
+          <t>501809</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>87,0%</t>
+          <t>86,58%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,28%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>24797</t>
+          <t>24124</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>48276</t>
+          <t>46684</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>121146</t>
+          <t>121541</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>169092</t>
+          <t>169876</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>153714</t>
+          <t>155055</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>207773</t>
+          <t>206130</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3228267</t>
+          <t>3229859</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3251746</t>
+          <t>3252419</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3210105</t>
+          <t>3209321</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3258051</t>
+          <t>3257656</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6447968</t>
+          <t>6449611</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6502027</t>
+          <t>6500686</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,67%</t>
         </is>
       </c>
     </row>
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>947</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12388</t>
+          <t>13054</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>943</t>
+          <t>948</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12148</t>
+          <t>13251</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,02%</t>
         </is>
       </c>
     </row>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>597867</t>
+          <t>597201</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>609305</t>
+          <t>609308</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1285194</t>
+          <t>1284091</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1296399</t>
+          <t>1296394</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6788</t>
+          <t>6124</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4473,7 +4473,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5988</t>
+          <t>6819</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,49%</t>
         </is>
       </c>
     </row>
@@ -4546,7 +4546,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>702786</t>
+          <t>703450</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1385449</t>
+          <t>1384618</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4746,7 +4746,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5067</t>
+          <t>4116</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8030</t>
+          <t>7256</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23565</t>
+          <t>23127</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8333</t>
+          <t>8423</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>23995</t>
+          <t>24653</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -4854,7 +4854,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>609550</t>
+          <t>610501</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>590699</t>
+          <t>591137</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>606234</t>
+          <t>607008</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1204885</t>
+          <t>1204227</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1220547</t>
+          <t>1220457</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,31%</t>
         </is>
       </c>
     </row>
@@ -5089,7 +5089,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4941</t>
+          <t>4935</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>25450</t>
+          <t>25249</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>48169</t>
+          <t>47847</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>25756</t>
+          <t>25614</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>50584</t>
+          <t>51856</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,91%</t>
         </is>
       </c>
     </row>
@@ -5197,7 +5197,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>424488</t>
+          <t>424494</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>399631</t>
+          <t>399953</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>422350</t>
+          <t>422551</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>89,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>826645</t>
+          <t>825373</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>851473</t>
+          <t>851615</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,08%</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5300</t>
+          <t>4860</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>21970</t>
+          <t>22281</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>44608</t>
+          <t>44554</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>21596</t>
+          <t>22438</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>44662</t>
+          <t>46514</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>7,01%</t>
         </is>
       </c>
     </row>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>304486</t>
+          <t>304926</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5555,7 +5555,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>309388</t>
+          <t>309442</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>332026</t>
+          <t>331715</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>87,41%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>619120</t>
+          <t>617268</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>642186</t>
+          <t>641344</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,62%</t>
         </is>
       </c>
     </row>
@@ -5775,7 +5775,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13591</t>
+          <t>13963</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>41678</t>
+          <t>41750</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>69509</t>
+          <t>70860</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>44041</t>
+          <t>43716</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>74666</t>
+          <t>74268</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,66%</t>
         </is>
       </c>
     </row>
@@ -5883,7 +5883,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>235257</t>
+          <t>234885</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -5898,7 +5898,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>318361</t>
+          <t>317010</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>346192</t>
+          <t>346120</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>82,08%</t>
+          <t>81,73%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>562052</t>
+          <t>562450</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>592677</t>
+          <t>593002</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>88,27%</t>
+          <t>88,34%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>93,13%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2057</t>
+          <t>2053</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>15112</t>
+          <t>16314</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>119238</t>
+          <t>119540</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>170426</t>
+          <t>170831</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6168,7 +6168,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>123147</t>
+          <t>124345</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>174630</t>
+          <t>175054</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3410664</t>
+          <t>3409462</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3423719</t>
+          <t>3423723</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,7 +6241,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3383564</t>
+          <t>3383159</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3434752</t>
+          <t>3434450</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6805136</t>
+          <t>6804712</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6856619</t>
+          <t>6855421</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,22%</t>
         </is>
       </c>
     </row>
@@ -7382,7 +7382,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5376</t>
+          <t>4587</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7397,7 +7397,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>935</t>
+          <t>946</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8501</t>
+          <t>8527</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1843</t>
+          <t>1842</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9824</t>
+          <t>10296</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7467,7 +7467,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,77%</t>
         </is>
       </c>
     </row>
@@ -7490,7 +7490,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>663721</t>
+          <t>664510</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -7505,7 +7505,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>652885</t>
+          <t>652859</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>660451</t>
+          <t>660440</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1320659</t>
+          <t>1320187</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1328640</t>
+          <t>1328641</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,7 +7575,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -7725,7 +7725,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7287</t>
+          <t>6828</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7740,7 +7740,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3208</t>
+          <t>3160</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15369</t>
+          <t>14448</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7775,7 +7775,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5257</t>
+          <t>4357</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>19035</t>
+          <t>18322</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -7833,7 +7833,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>638761</t>
+          <t>639220</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -7848,7 +7848,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>633708</t>
+          <t>634629</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>645869</t>
+          <t>645917</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,7 +7883,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1276090</t>
+          <t>1276803</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1289868</t>
+          <t>1290768</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,66%</t>
         </is>
       </c>
     </row>
@@ -8068,7 +8068,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6700</t>
+          <t>7766</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8083,7 +8083,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14045</t>
+          <t>14335</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>34520</t>
+          <t>35154</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15457</t>
+          <t>15257</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>36546</t>
+          <t>36346</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,73%</t>
         </is>
       </c>
     </row>
@@ -8176,7 +8176,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>471218</t>
+          <t>470152</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -8191,7 +8191,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>462329</t>
+          <t>461695</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>482804</t>
+          <t>482514</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>938221</t>
+          <t>938421</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>959310</t>
+          <t>959510</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,43%</t>
         </is>
       </c>
     </row>
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>33515</t>
+          <t>31391</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>58084</t>
+          <t>58239</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>32289</t>
+          <t>32444</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>59189</t>
+          <t>58354</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,19%</t>
         </is>
       </c>
     </row>
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>319678</t>
+          <t>319523</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>344247</t>
+          <t>346371</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>84,62%</t>
+          <t>84,58%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>652903</t>
+          <t>653738</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>679803</t>
+          <t>679648</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,44%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2706</t>
+          <t>2904</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>12355</t>
+          <t>13038</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>31090</t>
+          <t>31093</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>60895</t>
+          <t>61228</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8804,7 +8804,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>37397</t>
+          <t>36282</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>66696</t>
+          <t>68196</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,38%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>244643</t>
+          <t>243960</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>254292</t>
+          <t>254094</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>339274</t>
+          <t>338941</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>369079</t>
+          <t>369076</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,7 +8912,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>84,78%</t>
+          <t>84,7%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>590471</t>
+          <t>588971</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>619770</t>
+          <t>620885</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>89,62%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,48%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6004</t>
+          <t>6567</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>20052</t>
+          <t>20549</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>101099</t>
+          <t>100010</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>147982</t>
+          <t>146917</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>112228</t>
+          <t>111519</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>159314</t>
+          <t>158527</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,28%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3374298</t>
+          <t>3373801</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3388346</t>
+          <t>3387783</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>99,81%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3396560</t>
+          <t>3397625</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3443443</t>
+          <t>3444532</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6779578</t>
+          <t>6780365</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6826664</t>
+          <t>6827373</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,39%</t>
         </is>
       </c>
     </row>
@@ -9665,7 +9665,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>4077</t>
+          <t>3746</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -9675,12 +9675,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22398</t>
+          <t>18178</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9700,7 +9700,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2677</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -9710,7 +9710,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13620</t>
+          <t>15430</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,7 +9735,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>6754</t>
+          <t>6827</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -9745,12 +9745,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22833</t>
+          <t>25133</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,26%</t>
         </is>
       </c>
     </row>
@@ -9778,27 +9778,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>395910</t>
+          <t>404047</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>377589</t>
+          <t>389615</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -9813,17 +9813,17 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>310523</t>
+          <t>359431</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>299580</t>
+          <t>347082</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9833,7 +9833,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -9848,27 +9848,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>706433</t>
+          <t>763478</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>690354</t>
+          <t>745172</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10121,7 +10121,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -10156,7 +10156,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -10191,7 +10191,7 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,7 +10351,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2127</t>
+          <t>2277</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -10361,12 +10361,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7616</t>
+          <t>8003</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -10376,7 +10376,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1726</t>
+          <t>1784</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>462</t>
+          <t>486</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4688</t>
+          <t>5142</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>3853</t>
+          <t>4061</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1183</t>
+          <t>1594</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8731</t>
+          <t>9235</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>
@@ -10464,27 +10464,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>532890</t>
+          <t>617161</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>527401</t>
+          <t>611435</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>535017</t>
+          <t>619438</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>539302</t>
+          <t>618936</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>536340</t>
+          <t>615578</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>540566</t>
+          <t>620234</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,91%</t>
+          <t>99,92%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1072191</t>
+          <t>1236097</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1067313</t>
+          <t>1230923</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1074861</t>
+          <t>1238564</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,89%</t>
+          <t>99,87%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>535017</t>
+          <t>619438</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>535017</t>
+          <t>619438</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>535017</t>
+          <t>619438</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>541028</t>
+          <t>620720</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>541028</t>
+          <t>620720</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>541028</t>
+          <t>620720</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1076044</t>
+          <t>1240158</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1076044</t>
+          <t>1240158</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1076044</t>
+          <t>1240158</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2653</t>
+          <t>2698</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>733</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8368</t>
+          <t>8285</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10186</t>
+          <t>11977</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6519</t>
+          <t>7463</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15585</t>
+          <t>17966</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>12840</t>
+          <t>14674</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6861</t>
+          <t>9364</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>20336</t>
+          <t>21522</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>883028</t>
+          <t>695695</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>877313</t>
+          <t>690108</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>885681</t>
+          <t>697660</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>699242</t>
+          <t>720297</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>693843</t>
+          <t>714308</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>702909</t>
+          <t>724811</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1582269</t>
+          <t>1415992</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1574773</t>
+          <t>1409144</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1588248</t>
+          <t>1421302</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,35%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>885681</t>
+          <t>698393</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>885681</t>
+          <t>698393</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>885681</t>
+          <t>698393</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>709428</t>
+          <t>732274</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>709428</t>
+          <t>732274</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>709428</t>
+          <t>732274</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1595109</t>
+          <t>1430666</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1595109</t>
+          <t>1430666</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1595109</t>
+          <t>1430666</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>5685</t>
+          <t>5487</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2378</t>
+          <t>2289</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11318</t>
+          <t>10688</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>35366</t>
+          <t>39266</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>27637</t>
+          <t>31118</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>44467</t>
+          <t>49861</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>41051</t>
+          <t>44753</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>32272</t>
+          <t>34758</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>51541</t>
+          <t>55824</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,61%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>554552</t>
+          <t>602872</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>548919</t>
+          <t>597671</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>557859</t>
+          <t>606070</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>506147</t>
+          <t>564055</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>497046</t>
+          <t>553460</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>513876</t>
+          <t>572203</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1060699</t>
+          <t>1166927</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1050209</t>
+          <t>1155856</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1069478</t>
+          <t>1176922</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,13%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>560237</t>
+          <t>608359</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>560237</t>
+          <t>608359</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>560237</t>
+          <t>608359</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>541513</t>
+          <t>603321</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>541513</t>
+          <t>603321</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>541513</t>
+          <t>603321</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1101750</t>
+          <t>1211680</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1101750</t>
+          <t>1211680</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1101750</t>
+          <t>1211680</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5955</t>
+          <t>6322</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3089</t>
+          <t>3226</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10671</t>
+          <t>11115</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>40984</t>
+          <t>44779</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16113</t>
+          <t>35890</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>65264</t>
+          <t>55192</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>46939</t>
+          <t>51101</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>41675</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>63585</t>
+          <t>61706</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>7,33%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>360227</t>
+          <t>398518</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>355511</t>
+          <t>393725</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>363093</t>
+          <t>401614</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>565629</t>
+          <t>392407</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>541349</t>
+          <t>381994</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>590500</t>
+          <t>401296</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>89,76%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>87,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>925857</t>
+          <t>790924</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>909211</t>
+          <t>780319</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>948700</t>
+          <t>800350</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>95,05%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>366182</t>
+          <t>404840</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>366182</t>
+          <t>404840</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>366182</t>
+          <t>404840</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>606613</t>
+          <t>437186</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>606613</t>
+          <t>437186</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>606613</t>
+          <t>437186</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>972796</t>
+          <t>842025</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>972796</t>
+          <t>842025</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>972796</t>
+          <t>842025</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>7820</t>
+          <t>8977</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4227</t>
+          <t>4852</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13342</t>
+          <t>15944</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>69517</t>
+          <t>75886</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>59500</t>
+          <t>64965</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>80431</t>
+          <t>88281</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,27 +11793,27 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>77337</t>
+          <t>84864</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>66457</t>
+          <t>72431</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>90083</t>
+          <t>98540</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>274312</t>
+          <t>300609</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>268790</t>
+          <t>293642</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>277905</t>
+          <t>304734</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,32 +11871,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>354537</t>
+          <t>386824</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>343623</t>
+          <t>374429</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>364554</t>
+          <t>397745</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>83,6%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>81,03%</t>
+          <t>80,92%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>85,97%</t>
+          <t>85,96%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,22 +11906,22 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>628849</t>
+          <t>687432</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>616103</t>
+          <t>673756</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>639729</t>
+          <t>699865</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>89,01%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
@@ -11931,7 +11931,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>90,62%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282132</t>
+          <t>309586</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282132</t>
+          <t>309586</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282132</t>
+          <t>309586</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>424054</t>
+          <t>462710</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>424054</t>
+          <t>462710</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>424054</t>
+          <t>462710</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>706186</t>
+          <t>772296</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>706186</t>
+          <t>772296</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>706186</t>
+          <t>772296</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,22 +12066,22 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>28317</t>
+          <t>29507</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>19725</t>
+          <t>20019</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>45696</t>
+          <t>43297</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -12091,7 +12091,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>160456</t>
+          <t>176773</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>133684</t>
+          <t>156533</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>182674</t>
+          <t>197422</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>188773</t>
+          <t>206281</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>160015</t>
+          <t>183894</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>212931</t>
+          <t>231336</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -12179,27 +12179,27 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3424466</t>
+          <t>3495792</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3407087</t>
+          <t>3482002</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3433058</t>
+          <t>3505280</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3486884</t>
+          <t>3543033</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3464666</t>
+          <t>3522384</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3513656</t>
+          <t>3563273</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>6911351</t>
+          <t>7038824</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6887193</t>
+          <t>7013769</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6940109</t>
+          <t>7061211</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,46%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3452783</t>
+          <t>3525299</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3452783</t>
+          <t>3525299</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3452783</t>
+          <t>3525299</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3647340</t>
+          <t>3719806</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3647340</t>
+          <t>3719806</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3647340</t>
+          <t>3719806</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7100124</t>
+          <t>7245105</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7100124</t>
+          <t>7245105</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7100124</t>
+          <t>7245105</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
